--- a/docs/oc-regiones/suministro-de-combustibles/nuble.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M374"/>
+  <dimension ref="A1:M375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2220.75</v>
+        <v>2201.94</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3526.78</v>
+        <v>3496.91</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4809.25</v>
+        <v>4784.54</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10687.21</v>
+        <v>10632.3</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4274.89</v>
+        <v>4252.92</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>32061.64</v>
+        <v>31896.91</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7267.31</v>
+        <v>7229.97</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2244.32</v>
+        <v>2221.92</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41680.14</v>
+        <v>41264.16</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2671.8</v>
+        <v>2643.82</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7481.05</v>
+        <v>7402.71</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.64</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2671.8</v>
+        <v>2657.2</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5343.61</v>
+        <v>5284.07</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10687.21</v>
+        <v>10628.69</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2229.63</v>
+        <v>2236.96</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5343.61</v>
+        <v>5361.18</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6412.33</v>
+        <v>6523.02</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2229.63</v>
+        <v>2268.12</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2229.63</v>
+        <v>2245.08</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2670.73</v>
+        <v>2683.17</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2229.63</v>
+        <v>2240.01</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>16030.82</v>
+        <v>16105.48</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>10687.21</v>
+        <v>10764.26</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3740.53</v>
+        <v>3767.49</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10687.21</v>
+        <v>10764.26</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>20733.2</v>
+        <v>20647.74</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21374.43</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>10687.21</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6412.33</v>
+        <v>6445.44</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6519.2</v>
+        <v>6552.87</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4911.79</v>
+        <v>4848.3</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4366.04</v>
+        <v>4310.58</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10915.09</v>
+        <v>10776.44</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2292.17</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10915.08</v>
+        <v>10806.48</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10915.09</v>
+        <v>10806.49</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7640.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8732.07</v>
+        <v>8713.17</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4366.04</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>10915.09</v>
+        <v>10869.33</v>
       </c>
     </row>
     <row r="58">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2292.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7980.31</v>
+        <v>7912.71</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7640.56</v>
+        <v>7634.42</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>16372.63</v>
+        <v>16359.47</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2277.17</v>
+        <v>2285.91</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10915.09</v>
+        <v>10956.98</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6549.05</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10915.09</v>
+        <v>10956.98</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11460.84</v>
+        <v>11512.78</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>21469.12</v>
+        <v>21566.41</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6549.05</v>
+        <v>6578.73</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3846.46</v>
+        <v>3863.89</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2427.13</v>
+        <v>2433.57</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2277.17</v>
+        <v>2283.21</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2292.17</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2277.17</v>
+        <v>2273.98</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>10915.09</v>
+        <v>10929.08</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13971.31</v>
+        <v>14067.48</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3274.53</v>
+        <v>3297.07</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>48026.39</v>
+        <v>48356.96</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2728.77</v>
+        <v>2747.55</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2281.25</v>
+        <v>2300.75</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4366.04</v>
+        <v>4412.87</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>27768.95</v>
+        <v>28066.82</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4911.79</v>
+        <v>4972.16</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2728.77</v>
+        <v>2763.84</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3820.28</v>
+        <v>3869.37</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>9823.58</v>
+        <v>9949.809999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8609.549999999999</v>
+        <v>8656.629999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4892.79</v>
+        <v>4919.55</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11312.66</v>
+        <v>11023.78</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>11312.66</v>
+        <v>11023.78</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4525.06</v>
+        <v>4436.8</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4525.06</v>
+        <v>4436.8</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6787.59</v>
+        <v>6628.81</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>23190.95</v>
+        <v>22891.22</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>12443.92</v>
+        <v>12419.41</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2601.91</v>
+        <v>2601.93</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>11312.66</v>
+        <v>11312.73</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7918.86</v>
+        <v>7918.91</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>20362.78</v>
+        <v>20391.06</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>16968.98</v>
+        <v>16992.55</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2367.21</v>
+        <v>2370.49</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>11312.66</v>
+        <v>11304.93</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>11313.77</v>
+        <v>11306.05</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2375.66</v>
+        <v>2374.03</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2375.66</v>
+        <v>2374.03</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>11312.66</v>
+        <v>11304.93</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>45250.62</v>
+        <v>45095.32</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>22625.31</v>
+        <v>22505.8</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2367.21</v>
+        <v>2354.7</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3393.8</v>
+        <v>3375.87</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2367.21</v>
+        <v>2352.37</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>73532.25999999999</v>
+        <v>74522.48</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>39594.3</v>
+        <v>40197.08</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2828.16</v>
+        <v>2871.22</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7918.86</v>
+        <v>8119.05</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>28281.64</v>
+        <v>29139.23</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>101813.91</v>
+        <v>104840.12</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>11600.66</v>
+        <v>11559.36</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>22513.14</v>
+        <v>22432.98</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2668.15</v>
+        <v>2658.65</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>11600.66</v>
+        <v>11660.58</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11600.66</v>
+        <v>11660.58</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4640.26</v>
+        <v>4664.23</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4060.23</v>
+        <v>4081.2</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8352.469999999999</v>
+        <v>8395.620000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2900.16</v>
+        <v>2915.15</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.72</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>6960.4</v>
+        <v>6996.35</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2422.6</v>
+        <v>2429.25</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2900.16</v>
+        <v>2908.13</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2436.14</v>
+        <v>2458.3</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2552.14</v>
+        <v>2568.95</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10629.68</v>
+        <v>10699.69</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8932.51</v>
+        <v>8991.34</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.19</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>23201.32</v>
+        <v>23161.55</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2900.16</v>
+        <v>2897.17</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>11600.66</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2436.14</v>
+        <v>2418.69</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2436.14</v>
+        <v>2421.34</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>11600.66</v>
+        <v>11555.88</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>11600.66</v>
+        <v>11660.72</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>48357.32</v>
+        <v>49761.93</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2307.96</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3297.09</v>
+        <v>3392.86</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>22310.31</v>
+        <v>22398.27</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3846.61</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4615.93</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>6813.99</v>
+        <v>6926.29</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2747.58</v>
+        <v>2754.34</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2307.96</v>
+        <v>2313.64</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>10990.3</v>
+        <v>11017.34</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>10990.3</v>
+        <v>10848.81</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>32970.9</v>
+        <v>32738.23</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>7693.21</v>
+        <v>7638.92</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4396.12</v>
+        <v>4475.82</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2874.18</v>
+        <v>2926.29</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>13188.36</v>
+        <v>13187.68</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6594.18</v>
+        <v>6564.7</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>7693.21</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>5495.15</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>16485.45</v>
+        <v>16553.55</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2527.77</v>
+        <v>2520.8</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>10990.3</v>
+        <v>10826.38</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4396.12</v>
+        <v>4370.87</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4396.12</v>
+        <v>4370.87</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>4396.12</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>10990.3</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>12089.33</v>
+        <v>12037.25</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>32970.9</v>
+        <v>32828.86</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6594.18</v>
+        <v>6498.78</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2307.96</v>
+        <v>2274.57</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4396.12</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2304.3</v>
+        <v>2254.73</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>6594.18</v>
+        <v>6452.31</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>17584.48</v>
+        <v>17206.15</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>16485.45</v>
+        <v>16101.85</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>32743.57</v>
+        <v>31699.48</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2335.12</v>
+        <v>2289.07</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>10580.41</v>
+        <v>10371.75</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2338.83</v>
+        <v>2296.41</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>14478.45</v>
+        <v>14215.88</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>11137.27</v>
+        <v>10935.3</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8909.82</v>
+        <v>8671.24</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>11137.27</v>
+        <v>10839.05</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>23388.26</v>
+        <v>22762.01</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>35846.64</v>
+        <v>35995.62</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.42</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>5568.63</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>27843.17</v>
+        <v>27796.62</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>133647.23</v>
+        <v>133423.76</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>11137.27</v>
+        <v>11118.65</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2784.32</v>
+        <v>2821.38</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2450.2</v>
+        <v>2482.82</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>11137.27</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>16705.9</v>
+        <v>16928.3</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>11137.27</v>
+        <v>11282.61</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2335.12</v>
+        <v>2379.28</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4454.91</v>
+        <v>4539.16</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>22274.54</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>11137.27</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>16705.9</v>
+        <v>16895.89</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>7796.09</v>
+        <v>7884.75</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>5568.63</v>
+        <v>5604.25</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>14478.45</v>
+        <v>14571.05</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>11137.27</v>
+        <v>11172.31</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>38980.44</v>
+        <v>39103.09</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>16705.9</v>
+        <v>16758.47</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.72</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2784.32</v>
+        <v>2795.86</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2784.32</v>
+        <v>2790.09</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>11137.27</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>22274.54</v>
+        <v>22178.85</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>11140.35</v>
+        <v>11073.58</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3342.1</v>
+        <v>3322.08</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2339.47</v>
+        <v>2307.67</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5570.17</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5570.17</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2427.58</v>
+        <v>2394.57</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>28519.29</v>
+        <v>28276.04</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>10026.31</v>
+        <v>10080.31</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2562.28</v>
+        <v>2576.08</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3342.1</v>
+        <v>3379.48</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>11140.35</v>
+        <v>11224.73</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>16710.52</v>
+        <v>16837.1</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2785.09</v>
+        <v>2795.64</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2359.12</v>
+        <v>2368.06</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2785.09</v>
+        <v>2811.55</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>13368.42</v>
+        <v>13495.43</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5570.17</v>
+        <v>5623.1</v>
       </c>
     </row>
     <row r="257">
@@ -16132,7 +16132,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2785.09</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="258">
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.34</v>
       </c>
     </row>
     <row r="259">
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>13368.42</v>
+        <v>13468.01</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="261">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>14482.45</v>
+        <v>14590.35</v>
       </c>
     </row>
     <row r="262">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="263">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="264">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="265">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3342.1</v>
+        <v>3327.45</v>
       </c>
     </row>
     <row r="266">
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>22280.7</v>
+        <v>22183.03</v>
       </c>
     </row>
     <row r="267">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2693.16</v>
+        <v>2681.35</v>
       </c>
     </row>
     <row r="268">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>7798.24</v>
+        <v>7764.06</v>
       </c>
     </row>
     <row r="269">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>23394.73</v>
+        <v>23292.18</v>
       </c>
     </row>
     <row r="270">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>11140.35</v>
+        <v>11019.16</v>
       </c>
     </row>
     <row r="271">
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3342.1</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="272">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="273">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>6684.21</v>
+        <v>6669.04</v>
       </c>
     </row>
     <row r="274">
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2785.09</v>
+        <v>2798.77</v>
       </c>
     </row>
     <row r="275">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>16710.52</v>
+        <v>16765.96</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>6684.21</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>14482.45</v>
+        <v>14528.55</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2450.88</v>
+        <v>2458.68</v>
       </c>
     </row>
     <row r="279">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>11140.35</v>
+        <v>11199.59</v>
       </c>
     </row>
     <row r="280">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5570.17</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="281">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>7798.24</v>
+        <v>7839.71</v>
       </c>
     </row>
     <row r="282">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>11140.35</v>
+        <v>11199.59</v>
       </c>
     </row>
     <row r="283">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2767.37</v>
+        <v>2806.97</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5534.74</v>
+        <v>5613.94</v>
       </c>
     </row>
     <row r="285">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>14292.37</v>
+        <v>14496.88</v>
       </c>
     </row>
     <row r="286">
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5534.74</v>
+        <v>5599.67</v>
       </c>
     </row>
     <row r="287">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>8855.59</v>
+        <v>9005.360000000001</v>
       </c>
     </row>
     <row r="288">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2379.94</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="289">
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2379.94</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="290">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="291">
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3320.85</v>
+        <v>3354.62</v>
       </c>
     </row>
     <row r="292">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>33208.46</v>
+        <v>33546.17</v>
       </c>
     </row>
     <row r="293">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2767.37</v>
+        <v>2795.51</v>
       </c>
     </row>
     <row r="294">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>11069.49</v>
+        <v>11173.31</v>
       </c>
     </row>
     <row r="295">
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2435.29</v>
+        <v>2458.13</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>11069.49</v>
+        <v>11173.31</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>22526.4</v>
+        <v>22737.68</v>
       </c>
     </row>
     <row r="298">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2545.98</v>
+        <v>2569.86</v>
       </c>
     </row>
     <row r="299">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="300">
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>11069.49</v>
+        <v>10985.51</v>
       </c>
     </row>
     <row r="301">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2379.94</v>
+        <v>2361.88</v>
       </c>
     </row>
     <row r="302">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4427.79</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="303">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>66416.92</v>
+        <v>65294.75</v>
       </c>
     </row>
     <row r="304">
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2374.6</v>
+        <v>2334.48</v>
       </c>
     </row>
     <row r="305">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>5534.74</v>
+        <v>5456.19</v>
       </c>
     </row>
     <row r="306">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>16604.23</v>
+        <v>16368.58</v>
       </c>
     </row>
     <row r="307">
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>14390.33</v>
+        <v>14192.6</v>
       </c>
     </row>
     <row r="309">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>23245.92</v>
+        <v>22926.52</v>
       </c>
     </row>
     <row r="310">
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2379.94</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="311">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2767.37</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="312">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>4981.27</v>
+        <v>4950.39</v>
       </c>
     </row>
     <row r="313">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2767.37</v>
+        <v>2779.94</v>
       </c>
     </row>
     <row r="314">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>38743.2</v>
+        <v>38919.16</v>
       </c>
     </row>
     <row r="315">
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>16604.23</v>
+        <v>16851.47</v>
       </c>
     </row>
     <row r="316">
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2435.29</v>
+        <v>2471.55</v>
       </c>
     </row>
     <row r="317">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2374.6</v>
+        <v>2419.75</v>
       </c>
     </row>
     <row r="318">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3099.46</v>
+        <v>3158.38</v>
       </c>
     </row>
     <row r="319">
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>6641.69</v>
+        <v>6767.96</v>
       </c>
     </row>
     <row r="320">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>38743.2</v>
+        <v>39010.69</v>
       </c>
     </row>
     <row r="321">
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>11069.49</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="322">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>7748.64</v>
+        <v>7728.15</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5530.92</v>
+        <v>5516.29</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2767.37</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>5534.74</v>
+        <v>5426.41</v>
       </c>
     </row>
     <row r="326">
@@ -20341,13 +20341,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>11069.49</v>
+        <v>10841.99</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3881-502-CM26</t>
+          <t>1057506-4243-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20372,12 +20372,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20402,13 +20402,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>19334.67</v>
+        <v>2330.78</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1057506-4243-CM26</t>
+          <t>3881-502-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20433,12 +20433,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2308.85</v>
+        <v>19518.33</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2363.13</v>
+        <v>2385.57</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2685.37</v>
+        <v>2695.85</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>10741.48</v>
+        <v>10783.42</v>
       </c>
     </row>
     <row r="332">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2470.54</v>
+        <v>2480.19</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4296.59</v>
+        <v>4313.37</v>
       </c>
     </row>
     <row r="334">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>16112.23</v>
+        <v>16273.57</v>
       </c>
     </row>
     <row r="335">
@@ -20890,7 +20890,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3222.45</v>
+        <v>3238.87</v>
       </c>
     </row>
     <row r="336">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>16112.23</v>
+        <v>16194.33</v>
       </c>
     </row>
     <row r="337">
@@ -21012,13 +21012,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2363.13</v>
+        <v>2375.17</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4252-196-CM26</t>
+          <t>3905-146-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21043,12 +21043,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>72.529.500-6</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21073,13 +21073,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>19334.67</v>
+        <v>8626.639999999999</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3905-146-CM26</t>
+          <t>4252-196-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21104,12 +21104,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>72.529.500-6</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>19409.94</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="341">
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>13963.93</v>
+        <v>13893.19</v>
       </c>
     </row>
     <row r="342">
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2685.37</v>
+        <v>2671.77</v>
       </c>
     </row>
     <row r="343">
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>4833.67</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="344">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="345">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>10741.48</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.72</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.72</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>7519.04</v>
+        <v>7536.28</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="351">
@@ -21866,13 +21866,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>6444.89</v>
+        <v>6489.99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1040758-111-CM26</t>
+          <t>4158-181-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21892,17 +21892,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I.Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21927,13 +21927,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>11815.63</v>
+        <v>4283.02</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>3588-331-CM26</t>
+          <t>1040758-111-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -21953,17 +21953,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>10741.48</v>
+        <v>11778.31</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4158-181-CM26</t>
+          <t>3588-331-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22019,12 +22019,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>4296.59</v>
+        <v>10707.56</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="356">
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2363.13</v>
+        <v>2357.98</v>
       </c>
     </row>
     <row r="357">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>13426.86</v>
+        <v>13397.64</v>
       </c>
     </row>
     <row r="358">
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>23631.27</v>
+        <v>23583.89</v>
       </c>
     </row>
     <row r="359">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>10741.48</v>
+        <v>10679.31</v>
       </c>
     </row>
     <row r="360">
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.15</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>7519.04</v>
+        <v>7397.7</v>
       </c>
     </row>
     <row r="362">
@@ -22537,13 +22537,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>6444.89</v>
+        <v>6340.89</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3706-312-CM26</t>
+          <t>501-281-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22568,12 +22568,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22598,13 +22598,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>11815.63</v>
+        <v>2654.13</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>501-281-CM26</t>
+          <t>3784-380-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22629,12 +22629,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22659,13 +22659,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2685.37</v>
+        <v>10616.5</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3784-380-CM26</t>
+          <t>3706-312-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -22690,12 +22690,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>10741.48</v>
+        <v>11678.15</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2363.13</v>
+        <v>2350.03</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>4833.67</v>
+        <v>4806.87</v>
       </c>
     </row>
     <row r="368">
@@ -22903,13 +22903,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2685.37</v>
+        <v>2670.48</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>3497-422-CM26</t>
+          <t>3901-189-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -22964,13 +22964,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>13963.93</v>
+        <v>10688.67</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>3901-189-CM26</t>
+          <t>1057506-4420-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22990,17 +22990,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23025,13 +23025,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>10741.48</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1057506-4420-CM26</t>
+          <t>3497-422-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23051,17 +23051,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>3222.45</v>
+        <v>13895.27</v>
       </c>
     </row>
     <row r="372">
@@ -23147,13 +23147,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>10741.48</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1048606-23-CM26</t>
+          <t>3590-139-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>62.000.540-1</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SEREMI DESARROLLO SOCIAL REGION DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23208,13 +23208,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2308.85</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3590-139-CM26</t>
+          <t>1048606-23-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23239,12 +23239,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>62.000.540-1</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>SEREMI DESARROLLO SOCIAL REGION DE ÑUBLE</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23269,7 +23269,68 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2685.37</v>
+        <v>2324.3</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>5568-139-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>61.607.006-1</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>2711.14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/nuble.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M870"/>
+  <dimension ref="A1:M872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4674,7 +4674,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057512-255-CM25</t>
+          <t>3496-28-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4202.65</v>
+        <v>2626.66</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3496-28-CM25</t>
+          <t>1057512-255-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2626.66</v>
+        <v>4202.65</v>
       </c>
     </row>
     <row r="68">
@@ -6624,7 +6624,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5568-39-CM25</t>
+          <t>1051765-195-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6689,7 +6689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1051765-195-CM25</t>
+          <t>5568-39-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3784-2601-CM25</t>
+          <t>3881-237-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10893.6</v>
+        <v>19499.55</v>
       </c>
     </row>
     <row r="101">
@@ -7014,7 +7014,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3881-237-CM25</t>
+          <t>3784-2601-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>19499.55</v>
+        <v>10893.6</v>
       </c>
     </row>
     <row r="103">
@@ -7209,7 +7209,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>709413-1-CM25</t>
+          <t>5615-238-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2267.45</v>
+        <v>10797.39</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5615-238-CM25</t>
+          <t>709413-1-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7294,17 +7294,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10797.39</v>
+        <v>2267.45</v>
       </c>
     </row>
     <row r="107">
@@ -7469,7 +7469,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4594-192-CM25</t>
+          <t>3588-132-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>115607.56</v>
+        <v>10794.36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3588-132-CM25</t>
+          <t>4594-192-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>10794.36</v>
+        <v>115607.56</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1060500-9-CM25</t>
+          <t>4707-116-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3261.15</v>
+        <v>4348.2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3496-52-CM25</t>
+          <t>1060500-9-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2717.63</v>
+        <v>3261.15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4707-116-CM25</t>
+          <t>3496-52-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4348.2</v>
+        <v>2717.63</v>
       </c>
     </row>
     <row r="114">
@@ -7989,7 +7989,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3904-295-CM25</t>
+          <t>1036569-80-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8009,17 +8009,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,13 +8048,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7344.69</v>
+        <v>4196.96</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3590-57-CM25</t>
+          <t>3904-295-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8074,17 +8074,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5246.2</v>
+        <v>7344.69</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1036569-80-CM25</t>
+          <t>3590-57-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4196.96</v>
+        <v>5246.2</v>
       </c>
     </row>
     <row r="120">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3594-282-CM25</t>
+          <t>4157-299-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.140.200-2</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>40446.12</v>
+        <v>2072.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4157-299-CM25</t>
+          <t>3594-282-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.200-2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2072.03</v>
+        <v>40446.12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4123-131-CM25</t>
+          <t>4120-1965-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.140.301-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2147.04</v>
+        <v>2535.64</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4120-1965-CM25</t>
+          <t>4123-131-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.140.301-7</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2535.64</v>
+        <v>2147.04</v>
       </c>
     </row>
     <row r="133">
@@ -9289,7 +9289,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3747-101-CM25</t>
+          <t>3497-177-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7738.1</v>
+        <v>10317.47</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3497-177-CM25</t>
+          <t>3747-101-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>10317.47</v>
+        <v>7738.1</v>
       </c>
     </row>
     <row r="139">
@@ -9809,7 +9809,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4521-32-CM25</t>
+          <t>3706-141-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9829,17 +9829,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.250.602-2</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2157.8</v>
+        <v>10525.87</v>
       </c>
     </row>
     <row r="146">
@@ -10004,7 +10004,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3706-141-CM25</t>
+          <t>4521-32-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10024,17 +10024,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.250.602-2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>10525.87</v>
+        <v>2157.8</v>
       </c>
     </row>
     <row r="149">
@@ -10654,7 +10654,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4707-147-CM25</t>
+          <t>2471-762-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10674,17 +10674,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4782.4</v>
+        <v>2231.79</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2471-762-CM25</t>
+          <t>4707-147-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10739,17 +10739,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2231.79</v>
+        <v>4782.4</v>
       </c>
     </row>
     <row r="160">
@@ -10914,7 +10914,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1057506-1668-CM25</t>
+          <t>3600-65-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10934,17 +10934,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.140.201-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3192.61</v>
+        <v>3724.71</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3600-65-CM25</t>
+          <t>1057506-1668-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10999,17 +10999,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.140.201-0</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3724.71</v>
+        <v>3192.61</v>
       </c>
     </row>
     <row r="164">
@@ -11174,7 +11174,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4123-156-CM25</t>
+          <t>5615-368-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2250.18</v>
+        <v>10715.13</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1057511-550-CM25</t>
+          <t>3829-72-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11259,17 +11259,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3750.29</v>
+        <v>2201.96</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5615-368-CM25</t>
+          <t>3879-3113-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>10715.13</v>
+        <v>2206.72</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3879-3113-CM25</t>
+          <t>1057511-550-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2206.72</v>
+        <v>3750.29</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3829-72-CM25</t>
+          <t>4123-156-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2201.96</v>
+        <v>2250.18</v>
       </c>
     </row>
     <row r="171">
@@ -12084,7 +12084,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3784-2732-CM25</t>
+          <t>5568-74-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>10588.06</v>
+        <v>2647.02</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5568-74-CM25</t>
+          <t>3784-2732-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2647.02</v>
+        <v>10588.06</v>
       </c>
     </row>
     <row r="182">
@@ -12539,7 +12539,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3449-51-CM25</t>
+          <t>4707-188-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2985.3</v>
+        <v>4797.8</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4707-188-CM25</t>
+          <t>3449-51-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4797.8</v>
+        <v>2985.3</v>
       </c>
     </row>
     <row r="189">
@@ -13189,7 +13189,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3904-700-CM25</t>
+          <t>3829-94-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>7520.49</v>
+        <v>2256.15</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3829-94-CM25</t>
+          <t>3904-700-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2256.15</v>
+        <v>7520.49</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1057506-1823-CM25</t>
+          <t>4596-359-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2676.92</v>
+        <v>2216.49</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4596-359-CM25</t>
+          <t>1057506-1823-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2216.49</v>
+        <v>2676.92</v>
       </c>
     </row>
     <row r="201">
@@ -13644,7 +13644,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>229-380-CM25</t>
+          <t>1057124-17-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13664,17 +13664,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>62.000.600-9</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3203.9</v>
+        <v>6407.79</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1072229-55-CM25</t>
+          <t>1493-467-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13729,17 +13729,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.140.800-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3203.9</v>
+        <v>26699.13</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4158-161-CM25</t>
+          <t>229-380-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4271.86</v>
+        <v>3203.9</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1493-467-CM25</t>
+          <t>1072229-55-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13859,17 +13859,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.140.800-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>26699.13</v>
+        <v>3203.9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1057124-17-CM25</t>
+          <t>4158-161-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13924,17 +13924,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>62.000.600-9</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,7 +13963,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>6407.79</v>
+        <v>4271.86</v>
       </c>
     </row>
     <row r="209">
@@ -14619,7 +14619,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5615-504-CM25</t>
+          <t>3746-71-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>11130.43</v>
+        <v>3180.12</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3746-71-CM25</t>
+          <t>5615-504-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3180.12</v>
+        <v>11130.43</v>
       </c>
     </row>
     <row r="221">
@@ -14944,7 +14944,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3881-529-CM25</t>
+          <t>2471-1074-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14964,17 +14964,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>22230.75</v>
+        <v>2239.07</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2471-1074-CM25</t>
+          <t>3881-529-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15029,17 +15029,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2239.07</v>
+        <v>22230.75</v>
       </c>
     </row>
     <row r="226">
@@ -15334,7 +15334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3786-1762-CM25</t>
+          <t>3497-290-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15354,17 +15354,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2256.44</v>
+        <v>10744.95</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3497-290-CM25</t>
+          <t>3786-1762-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15419,17 +15419,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>10744.95</v>
+        <v>2256.44</v>
       </c>
     </row>
     <row r="232">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3905-156-CM25</t>
+          <t>4519-225-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>72.529.500-6</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>8580.559999999999</v>
+        <v>6435.42</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4519-225-CM25</t>
+          <t>3905-156-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>72.529.500-6</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,7 +15913,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>6435.42</v>
+        <v>8580.559999999999</v>
       </c>
     </row>
     <row r="239">
@@ -16244,7 +16244,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1057513-440-CM25</t>
+          <t>3784-2783-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5169.45</v>
+        <v>10338.91</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4123-254-CM25</t>
+          <t>1113015-195-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2171.17</v>
+        <v>2137.77</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4252-224-CM25</t>
+          <t>4123-254-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16394,17 +16394,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5583.01</v>
+        <v>2171.17</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3784-2783-CM25</t>
+          <t>1057513-440-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>10338.91</v>
+        <v>5169.45</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1113015-195-CM25</t>
+          <t>4252-224-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,7 +16563,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2137.77</v>
+        <v>5583.01</v>
       </c>
     </row>
     <row r="249">
@@ -16699,7 +16699,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3901-126-CM25</t>
+          <t>4328-667-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16719,17 +16719,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9359.889999999999</v>
+        <v>5199.94</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1294449-64-CM25</t>
+          <t>3901-126-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16784,17 +16784,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>36399.56</v>
+        <v>9359.889999999999</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4328-667-CM25</t>
+          <t>1294449-64-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ñiquen</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5199.94</v>
+        <v>36399.56</v>
       </c>
     </row>
     <row r="254">
@@ -16959,7 +16959,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3497-316-CM25</t>
+          <t>3659-568-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>10453.14</v>
+        <v>31359.43</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3659-568-CM25</t>
+          <t>3497-316-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>31359.43</v>
+        <v>10453.14</v>
       </c>
     </row>
     <row r="257">
@@ -18064,7 +18064,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3881-631-CM25</t>
+          <t>2471-1399-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18084,17 +18084,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>18511.22</v>
+        <v>2177.79</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2471-1399-CM25</t>
+          <t>3841-140-CM25</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18149,17 +18149,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2177.79</v>
+        <v>10370.43</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3841-140-CM25</t>
+          <t>3881-631-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>10370.43</v>
+        <v>18511.22</v>
       </c>
     </row>
     <row r="275">
@@ -18519,7 +18519,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3904-1041-CM25</t>
+          <t>3449-96-CM25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7202.54</v>
+        <v>2572.33</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3449-96-CM25</t>
+          <t>3904-1041-CM25</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,7 +18643,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2572.33</v>
+        <v>7202.54</v>
       </c>
     </row>
     <row r="281">
@@ -18714,7 +18714,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>501-329-CM25</t>
+          <t>5615-640-CM25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2182.32</v>
+        <v>10391.99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3786-1798-CM25</t>
+          <t>501-329-CM25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18799,17 +18799,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5615-640-CM25</t>
+          <t>3786-1798-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18864,17 +18864,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>10391.99</v>
+        <v>2182.32</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1254-21-CM25</t>
+          <t>1155683-206-CM25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>60.805.015-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2141.73</v>
+        <v>15595.1</v>
       </c>
     </row>
     <row r="286">
@@ -19039,7 +19039,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1155683-206-CM25</t>
+          <t>4158-233-CM25</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19059,17 +19059,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>15595.1</v>
+        <v>4158.7</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4158-233-CM25</t>
+          <t>1254-21-CM25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19124,17 +19124,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>60.805.015-9</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>4158.7</v>
+        <v>2141.73</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1057508-2340-CM25</t>
+          <t>4123-309-CM25</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>31048.19</v>
+        <v>2173.37</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3496-161-CM25</t>
+          <t>3784-2847-CM25</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19254,17 +19254,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,13 +19293,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2587.35</v>
+        <v>10349.4</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>4120-2122-CM25</t>
+          <t>3588-360-CM25</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.140.301-7</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2587.35</v>
+        <v>10349.4</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3784-2847-CM25</t>
+          <t>4520-186-CM25</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19384,17 +19384,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.266.400-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>10349.4</v>
+        <v>2587.35</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3588-360-CM25</t>
+          <t>1057508-2340-CM25</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19449,17 +19449,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19488,13 +19488,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>10349.4</v>
+        <v>31048.19</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4123-309-CM25</t>
+          <t>4120-2122-CM25</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19514,12 +19514,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.140.301-7</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2173.37</v>
+        <v>2587.35</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4520-186-CM25</t>
+          <t>3496-161-CM25</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.266.400-0</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -20014,7 +20014,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3600-141-CM25</t>
+          <t>4328-834-CM25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20039,12 +20039,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.140.201-0</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3636.33</v>
+        <v>5194.75</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1057511-950-CM25</t>
+          <t>3600-141-CM25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20099,17 +20099,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.140.201-0</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20144,7 +20144,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4328-834-CM25</t>
+          <t>1057511-950-CM25</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20164,17 +20164,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ñiquen</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,13 +20203,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>5194.75</v>
+        <v>3636.33</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4521-94-CM25</t>
+          <t>1057513-528-CM25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20229,17 +20229,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>69.250.602-2</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2176.14</v>
+        <v>5181.29</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3706-376-CM25</t>
+          <t>4521-94-CM25</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20294,17 +20294,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.250.602-2</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>10362.59</v>
+        <v>2176.14</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1057513-528-CM25</t>
+          <t>3706-376-CM25</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20398,13 +20398,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>5181.29</v>
+        <v>10362.59</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4707-325-CM25</t>
+          <t>1011183-139-CM25</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20424,17 +20424,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>4645.69</v>
+        <v>3909.88</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1011183-139-CM25</t>
+          <t>4519-278-CM25</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20489,17 +20489,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,13 +20528,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3909.88</v>
+        <v>6194.25</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4519-278-CM25</t>
+          <t>4707-325-CM25</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20559,12 +20559,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,7 +20593,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>6194.25</v>
+        <v>4645.69</v>
       </c>
     </row>
     <row r="311">
@@ -21184,7 +21184,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1057506-2234-CM25</t>
+          <t>3785-282-CM25</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2578.76</v>
+        <v>2166.15</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3785-282-CM25</t>
+          <t>1057506-2234-CM25</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21274,12 +21274,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21308,7 +21308,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2166.15</v>
+        <v>2578.76</v>
       </c>
     </row>
     <row r="322">
@@ -21444,7 +21444,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3841-173-CM25</t>
+          <t>1051765-870-CM25</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21464,17 +21464,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>10340.51</v>
+        <v>6204.31</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1051765-870-CM25</t>
+          <t>3841-173-CM25</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21529,17 +21529,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21568,7 +21568,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>6204.31</v>
+        <v>10340.51</v>
       </c>
     </row>
     <row r="326">
@@ -21769,7 +21769,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1057508-2454-CM25</t>
+          <t>5615-739-CM25</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21789,17 +21789,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,13 +21828,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>20932.11</v>
+        <v>5233.03</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5615-739-CM25</t>
+          <t>1057508-2454-CM25</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21854,17 +21854,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21893,7 +21893,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>5233.03</v>
+        <v>20932.11</v>
       </c>
     </row>
     <row r="331">
@@ -21964,7 +21964,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3496-196-CM25</t>
+          <t>5568-154-CM25</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21984,17 +21984,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2618.95</v>
+        <v>2199.92</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5568-154-CM25</t>
+          <t>4157-1052-CM25</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22049,17 +22049,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2199.92</v>
+        <v>2176.82</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4157-1052-CM25</t>
+          <t>3496-196-CM25</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2176.82</v>
+        <v>2618.95</v>
       </c>
     </row>
     <row r="335">
@@ -23589,7 +23589,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>3706-465-CM25</t>
+          <t>1057506-2345-CM25</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23614,12 +23614,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23648,13 +23648,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>12458.86</v>
+        <v>2595.6</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1057506-2345-CM25</t>
+          <t>3588-457-CM25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23674,17 +23674,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2595.6</v>
+        <v>10901.5</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3588-457-CM25</t>
+          <t>3706-465-CM25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23739,17 +23739,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>10901.5</v>
+        <v>12458.86</v>
       </c>
     </row>
     <row r="360">
@@ -24174,7 +24174,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>3841-202-CM25</t>
+          <t>3841-200-CM25</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>10376.78</v>
+        <v>2179.12</v>
       </c>
     </row>
     <row r="367">
@@ -24304,7 +24304,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3841-200-CM25</t>
+          <t>3841-202-CM25</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24363,13 +24363,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2179.12</v>
+        <v>10376.78</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1036569-193-CM25</t>
+          <t>1057513-639-CM25</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24389,17 +24389,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24428,13 +24428,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>4169.45</v>
+        <v>3127.08</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1057513-639-CM25</t>
+          <t>3497-452-CM25</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24454,17 +24454,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24493,13 +24493,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3127.08</v>
+        <v>10423.62</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>3497-452-CM25</t>
+          <t>1036569-193-CM25</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24524,12 +24524,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>10423.62</v>
+        <v>4169.45</v>
       </c>
     </row>
     <row r="372">
@@ -24629,7 +24629,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5615-785-CM25</t>
+          <t>1040758-153-CM25</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24654,12 +24654,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24694,7 +24694,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1040758-153-CM25</t>
+          <t>5615-785-CM25</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24719,12 +24719,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24759,7 +24759,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>501-467-CM25</t>
+          <t>4123-406-CM25</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24779,17 +24779,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24824,7 +24824,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>4123-406-CM25</t>
+          <t>501-467-CM25</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24844,17 +24844,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -25019,7 +25019,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>4519-352-CM25</t>
+          <t>3600-195-CM25</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -25044,12 +25044,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.140.201-0</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -25078,13 +25078,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>6303.98</v>
+        <v>3677.32</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>3600-195-CM25</t>
+          <t>4157-1192-CM25</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -25109,12 +25109,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>69.140.201-0</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -25143,13 +25143,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>3677.32</v>
+        <v>2183.23</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4157-1192-CM25</t>
+          <t>1493-883-CM25</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -25174,12 +25174,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.800-0</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -25208,13 +25208,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2183.23</v>
+        <v>9455.969999999999</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1493-883-CM25</t>
+          <t>4519-352-CM25</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25239,12 +25239,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.140.800-0</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25273,7 +25273,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>9455.969999999999</v>
+        <v>6303.98</v>
       </c>
     </row>
     <row r="383">
@@ -25799,7 +25799,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1057512-1224-CM25</t>
+          <t>4256-4638-CM25</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25819,17 +25819,17 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25858,13 +25858,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>4252.74</v>
+        <v>5315.93</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4256-4638-CM25</t>
+          <t>1057512-1224-CM25</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25884,17 +25884,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25923,7 +25923,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>5315.93</v>
+        <v>4252.74</v>
       </c>
     </row>
     <row r="393">
@@ -26969,7 +26969,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>3841-222-CM25</t>
+          <t>4120-2200-CM25</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26994,12 +26994,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.140.301-7</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,13 +27028,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>10628.69</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>4120-2200-CM25</t>
+          <t>3841-222-CM25</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>69.140.301-7</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2232.02</v>
+        <v>10628.69</v>
       </c>
     </row>
     <row r="411">
@@ -27879,7 +27879,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1254-27-CM25</t>
+          <t>501-498-CM25</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27899,17 +27899,17 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>60.805.015-9</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>2240.01</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="424">
@@ -28009,7 +28009,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1493-951-CM25</t>
+          <t>1254-27-CM25</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28029,17 +28029,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.140.800-0</t>
+          <t>60.805.015-9</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>16105.48</v>
+        <v>2240.01</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>501-498-CM25</t>
+          <t>1493-951-CM25</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28099,12 +28099,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.800-0</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -28133,13 +28133,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2254.77</v>
+        <v>16105.48</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>3588-525-CM25</t>
+          <t>1057513-708-CM25</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -28164,12 +28164,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -28198,13 +28198,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>10764.26</v>
+        <v>3767.49</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>3496-259-CM25</t>
+          <t>3497-482-CM25</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -28263,13 +28263,13 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>2691.07</v>
+        <v>10764.26</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1057513-708-CM25</t>
+          <t>3588-525-CM25</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28294,12 +28294,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28328,13 +28328,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>3767.49</v>
+        <v>10764.26</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>3497-482-CM25</t>
+          <t>3496-259-CM25</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>10764.26</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="431">
@@ -28919,7 +28919,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1057506-2498-CM25</t>
+          <t>4367-599-CM25</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28939,17 +28939,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.972.800-9</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,7 +28978,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2263.05</v>
+        <v>10776.44</v>
       </c>
     </row>
     <row r="440">
@@ -29049,7 +29049,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>4367-599-CM25</t>
+          <t>1057506-2498-CM25</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -29069,17 +29069,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.972.800-9</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -29108,7 +29108,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>10776.44</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="442">
@@ -34379,7 +34379,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1057512-125-CM26</t>
+          <t>3706-19-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -34404,12 +34404,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -34438,13 +34438,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>4664.23</v>
+        <v>11660.58</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2129-21-CM26</t>
+          <t>1035180-5-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>11660.58</v>
+        <v>4081.2</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>3706-19-CM26</t>
+          <t>3747-30-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -34568,7 +34568,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>11660.58</v>
+        <v>8395.620000000001</v>
       </c>
     </row>
     <row r="526">
@@ -34769,7 +34769,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1035180-5-CM26</t>
+          <t>2129-21-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -34828,13 +34828,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>4081.2</v>
+        <v>11660.58</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>3747-30-CM26</t>
+          <t>1057512-125-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34854,17 +34854,17 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -34893,7 +34893,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>8395.620000000001</v>
+        <v>4664.23</v>
       </c>
     </row>
     <row r="531">
@@ -36654,7 +36654,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>3904-118-CM26</t>
+          <t>2724-147-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36674,17 +36674,17 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -36713,13 +36713,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>7638.92</v>
+        <v>32738.23</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2724-147-CM26</t>
+          <t>3904-118-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36739,17 +36739,17 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -36778,13 +36778,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>32738.23</v>
+        <v>7638.92</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>1700-17-CM26</t>
+          <t>4707-76-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36809,12 +36809,12 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -36843,13 +36843,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2926.29</v>
+        <v>4475.82</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>4707-76-CM26</t>
+          <t>1700-17-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36874,12 +36874,12 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -36908,7 +36908,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>4475.82</v>
+        <v>2926.29</v>
       </c>
     </row>
     <row r="562">
@@ -37044,7 +37044,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>3590-37-CM26</t>
+          <t>3829-12-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -37064,17 +37064,17 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -37103,13 +37103,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>5499.88</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>3829-12-CM26</t>
+          <t>3590-37-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37129,17 +37129,17 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -37168,7 +37168,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>7699.84</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="566">
@@ -37564,7 +37564,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>501-94-CM26</t>
+          <t>3497-150-CM26</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -37584,17 +37584,17 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -37623,13 +37623,13 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2293.18</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>3497-150-CM26</t>
+          <t>709413-4-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -37654,12 +37654,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -37688,13 +37688,13 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>10919.89</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>709413-4-CM26</t>
+          <t>4120-41-CM26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -37714,17 +37714,17 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.140.301-7</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -37753,13 +37753,13 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>4367.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>4120-41-CM26</t>
+          <t>501-94-CM26</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -37784,12 +37784,12 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>69.140.301-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -37824,7 +37824,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>3784-174-CM26</t>
+          <t>1294449-22-CM26</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -37844,17 +37844,17 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -37883,13 +37883,13 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>10942.95</v>
+        <v>32828.86</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>1294449-22-CM26</t>
+          <t>3784-174-CM26</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37909,17 +37909,17 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -37948,7 +37948,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>32828.86</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="578">
@@ -38799,7 +38799,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>3497-176-CM26</t>
+          <t>1057512-310-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -38824,12 +38824,12 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -38858,13 +38858,13 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>14215.88</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>1057512-310-CM26</t>
+          <t>3786-21-CM26</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -38889,12 +38889,12 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -38923,13 +38923,13 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>3280.59</v>
+        <v>2296.41</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>3786-21-CM26</t>
+          <t>3497-176-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38954,12 +38954,12 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -38988,13 +38988,13 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2296.41</v>
+        <v>14215.88</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>3841-40-CM26</t>
+          <t>1173801-5-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -39014,17 +39014,17 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -39053,13 +39053,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>10839.05</v>
+        <v>2276.2</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>1173801-5-CM26</t>
+          <t>3905-68-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -39079,17 +39079,17 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>72.529.500-6</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -39118,13 +39118,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2276.2</v>
+        <v>8671.24</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>3905-68-CM26</t>
+          <t>3841-40-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -39149,12 +39149,12 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>72.529.500-6</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -39183,7 +39183,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>8671.24</v>
+        <v>10839.05</v>
       </c>
     </row>
     <row r="597">
@@ -39839,7 +39839,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>4328-366-CM26</t>
+          <t>1057511-514-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -39859,17 +39859,17 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ñiquen</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -39898,13 +39898,13 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>11285.54</v>
+        <v>2821.38</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1057511-514-CM26</t>
+          <t>3600-50-CM26</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -39924,17 +39924,17 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.140.201-0</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -39963,13 +39963,13 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2821.38</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>3600-50-CM26</t>
+          <t>4328-366-CM26</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -39994,12 +39994,12 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>69.140.201-0</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -40028,7 +40028,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>5642.77</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="610">
@@ -40749,7 +40749,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2724-294-CM26</t>
+          <t>3904-319-CM26</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -40774,12 +40774,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -40808,7 +40808,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>16758.47</v>
+        <v>11172.31</v>
       </c>
     </row>
     <row r="622">
@@ -40879,7 +40879,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>3904-319-CM26</t>
+          <t>2724-294-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -40904,12 +40904,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -40938,7 +40938,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>11172.31</v>
+        <v>16758.47</v>
       </c>
     </row>
     <row r="624">
@@ -41074,7 +41074,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>3588-170-CM26</t>
+          <t>3496-78-CM26</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -41094,17 +41094,17 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -41133,13 +41133,13 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>11160.34</v>
+        <v>2790.09</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>3496-78-CM26</t>
+          <t>3588-170-CM26</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -41159,17 +41159,17 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -41198,7 +41198,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>2790.09</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="628">
@@ -41269,7 +41269,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>1057509-5003-CM26</t>
+          <t>1051765-340-CM26</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -41289,17 +41289,17 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -41309,17 +41309,17 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
@@ -41328,13 +41328,13 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>5494.45</v>
+        <v>2307.67</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>1700-33-CM26</t>
+          <t>4707-143-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -41359,12 +41359,12 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -41393,13 +41393,13 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2394.57</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1051765-340-CM26</t>
+          <t>1057509-5003-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41419,17 +41419,17 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -41439,17 +41439,17 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -41458,13 +41458,13 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2307.67</v>
+        <v>5494.45</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>4707-143-CM26</t>
+          <t>1700-33-CM26</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -41489,12 +41489,12 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -41523,7 +41523,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>5494.45</v>
+        <v>2394.57</v>
       </c>
     </row>
     <row r="633">
@@ -41789,7 +41789,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>3841-51-CM26</t>
+          <t>1493-321-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -41814,12 +41814,12 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.140.800-0</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -41848,13 +41848,13 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>11224.73</v>
+        <v>16837.1</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>1493-321-CM26</t>
+          <t>3841-51-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -41879,12 +41879,12 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>69.140.800-0</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -41913,7 +41913,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>16837.1</v>
+        <v>11224.73</v>
       </c>
     </row>
     <row r="639">
@@ -42569,7 +42569,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>1057513-265-CM26</t>
+          <t>4158-110-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -42589,17 +42589,17 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -42634,7 +42634,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>4158-110-CM26</t>
+          <t>1057513-265-CM26</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -42654,17 +42654,17 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -42829,7 +42829,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>3871-96-CM26</t>
+          <t>3871-99-CM26</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -42888,7 +42888,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>22183.03</v>
+        <v>2681.35</v>
       </c>
     </row>
     <row r="654">
@@ -43024,7 +43024,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>3871-99-CM26</t>
+          <t>3871-96-CM26</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -43083,13 +43083,13 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2681.35</v>
+        <v>22183.03</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>5568-90-CM26</t>
+          <t>4120-114-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -43109,17 +43109,17 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>69.140.301-7</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -43148,13 +43148,13 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>2754.79</v>
+        <v>3305.75</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>3784-275-CM26</t>
+          <t>5568-90-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -43179,12 +43179,12 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -43213,13 +43213,13 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>11019.16</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>4120-114-CM26</t>
+          <t>3784-275-CM26</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -43239,17 +43239,17 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>69.140.301-7</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -43278,7 +43278,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>3305.75</v>
+        <v>11019.16</v>
       </c>
     </row>
     <row r="660">
@@ -43869,7 +43869,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>3600-84-CM26</t>
+          <t>1057510-2045-CM26</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -43894,12 +43894,12 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>69.140.201-0</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -43928,13 +43928,13 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>5613.94</v>
+        <v>14496.88</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>1057510-2045-CM26</t>
+          <t>3496-107-CM26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -43959,12 +43959,12 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>14496.88</v>
+        <v>2806.97</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>3496-107-CM26</t>
+          <t>3600-84-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -44024,12 +44024,12 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.140.201-0</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -44058,7 +44058,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>2806.97</v>
+        <v>5613.94</v>
       </c>
     </row>
     <row r="672">
@@ -44129,7 +44129,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>1375761-848-CM26</t>
+          <t>4256-160-CM26</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -44149,17 +44149,17 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>11256.7</v>
+        <v>9005.360000000001</v>
       </c>
     </row>
     <row r="674">
@@ -44324,7 +44324,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>4256-160-CM26</t>
+          <t>3706-213-CM26</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -44344,17 +44344,17 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -44383,13 +44383,13 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>9005.360000000001</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>3706-213-CM26</t>
+          <t>1375761-848-CM26</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -44414,12 +44414,12 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -44909,7 +44909,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>3841-76-CM26</t>
+          <t>3905-130-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44934,12 +44934,12 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>72.529.500-6</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -44968,13 +44968,13 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>10985.51</v>
+        <v>2361.88</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>3905-130-CM26</t>
+          <t>4364-293-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -44999,12 +44999,12 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>72.529.500-6</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -45033,13 +45033,13 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>2361.88</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>4364-293-CM26</t>
+          <t>1057512-484-CM26</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -45059,17 +45059,17 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -45098,13 +45098,13 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>4394.2</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>1057512-484-CM26</t>
+          <t>3841-76-CM26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -45124,17 +45124,17 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -45163,7 +45163,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>3295.65</v>
+        <v>10985.51</v>
       </c>
     </row>
     <row r="689">
@@ -45429,7 +45429,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>3829-67-CM26</t>
+          <t>4157-499-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -45454,12 +45454,12 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -45488,13 +45488,13 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>3275.22</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>3497-319-CM26</t>
+          <t>1057511-773-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -45519,12 +45519,12 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -45553,13 +45553,13 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>14192.6</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>1057511-773-CM26</t>
+          <t>5615-373-CM26</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -45579,17 +45579,17 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -45618,13 +45618,13 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2347.24</v>
+        <v>22926.52</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>4157-499-CM26</t>
+          <t>3497-319-CM26</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -45644,17 +45644,17 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -45683,13 +45683,13 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2729.35</v>
+        <v>14192.6</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>5615-373-CM26</t>
+          <t>3829-67-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -45714,12 +45714,12 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -45748,7 +45748,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>22926.52</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="698">
@@ -46274,7 +46274,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>3784-305-CM26</t>
+          <t>1057508-1859-CM26</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -46299,12 +46299,12 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -46333,13 +46333,13 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>11145.91</v>
+        <v>39010.69</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1057508-1859-CM26</t>
+          <t>3784-305-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -46364,12 +46364,12 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -46398,7 +46398,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>39010.69</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="708">
@@ -46469,7 +46469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1233616-1139-CM26</t>
+          <t>5568-101-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -46494,12 +46494,12 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -46528,13 +46528,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>5516.29</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>5568-101-CM26</t>
+          <t>1233616-1139-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -46559,12 +46559,12 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -46593,7 +46593,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>2760.05</v>
+        <v>5516.29</v>
       </c>
     </row>
     <row r="711">
@@ -46859,7 +46859,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>4596-501-CM26</t>
+          <t>3881-502-CM26</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -46884,12 +46884,12 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -46918,13 +46918,13 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>2385.57</v>
+        <v>19518.33</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>1057506-4242-CM26</t>
+          <t>4596-501-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -46944,17 +46944,17 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -46983,13 +46983,13 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2330.78</v>
+        <v>2385.57</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>1057506-4243-CM26</t>
+          <t>1057506-4242-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -47054,7 +47054,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>3881-502-CM26</t>
+          <t>1057506-4243-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -47074,17 +47074,17 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -47113,13 +47113,13 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>19518.33</v>
+        <v>2330.78</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>1057511-922-CM26</t>
+          <t>3496-124-CM26</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -47144,12 +47144,12 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -47178,7 +47178,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>4313.37</v>
+        <v>2695.85</v>
       </c>
     </row>
     <row r="720">
@@ -47249,7 +47249,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>3496-124-CM26</t>
+          <t>1057511-922-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -47274,12 +47274,12 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -47308,7 +47308,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>2695.85</v>
+        <v>4313.37</v>
       </c>
     </row>
     <row r="722">
@@ -47639,7 +47639,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>3905-146-CM26</t>
+          <t>3829-78-CM26</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -47664,12 +47664,12 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>72.529.500-6</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -47698,13 +47698,13 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>8626.639999999999</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>4252-196-CM26</t>
+          <t>3905-146-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -47729,12 +47729,12 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>72.529.500-6</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -47763,13 +47763,13 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>19409.94</v>
+        <v>8626.639999999999</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>3829-78-CM26</t>
+          <t>4252-196-CM26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -47794,12 +47794,12 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -47828,7 +47828,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>3234.99</v>
+        <v>19409.94</v>
       </c>
     </row>
     <row r="730">
@@ -47964,7 +47964,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>1049242-38-CM26</t>
+          <t>3841-109-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -47984,17 +47984,17 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -48023,7 +48023,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>4843.97</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="733">
@@ -48094,7 +48094,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>3841-109-CM26</t>
+          <t>1049242-38-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -48114,17 +48114,17 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -48153,13 +48153,13 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>10764.38</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>4520-118-CM26</t>
+          <t>3747-200-CM26</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -48184,12 +48184,12 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>69.266.400-0</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -48218,13 +48218,13 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>2314.72</v>
+        <v>7536.28</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>3747-200-CM26</t>
+          <t>4520-118-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -48249,12 +48249,12 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.266.400-0</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -48283,7 +48283,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>7536.28</v>
+        <v>2314.72</v>
       </c>
     </row>
     <row r="737">
@@ -48549,7 +48549,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>4158-181-CM26</t>
+          <t>3588-331-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -48574,12 +48574,12 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -48608,13 +48608,13 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>4283.02</v>
+        <v>10707.56</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>3588-331-CM26</t>
+          <t>1057506-4345-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48634,17 +48634,17 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -48673,13 +48673,13 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>10707.56</v>
+        <v>2301.56</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>1057506-4345-CM26</t>
+          <t>1040758-111-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -48704,12 +48704,12 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -48738,13 +48738,13 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>2301.56</v>
+        <v>11778.31</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>1040758-111-CM26</t>
+          <t>4158-181-CM26</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -48764,17 +48764,17 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -48803,13 +48803,13 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>11778.31</v>
+        <v>4283.02</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>1155683-92-CM26</t>
+          <t>4329-434-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -48829,17 +48829,17 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -48868,13 +48868,13 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>13397.64</v>
+        <v>2357.98</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>4329-434-CM26</t>
+          <t>1155683-92-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48894,17 +48894,17 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ñiquen</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -48933,7 +48933,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2357.98</v>
+        <v>13397.64</v>
       </c>
     </row>
     <row r="747">
@@ -49199,7 +49199,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>1051765-649-CM26</t>
+          <t>4707-248-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -49219,17 +49219,17 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -49258,13 +49258,13 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>7397.7</v>
+        <v>6340.89</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>4707-248-CM26</t>
+          <t>1051765-649-CM26</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -49284,17 +49284,17 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -49323,13 +49323,13 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>6340.89</v>
+        <v>7397.7</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>501-281-CM26</t>
+          <t>3706-312-CM26</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -49349,17 +49349,17 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -49388,7 +49388,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>2654.13</v>
+        <v>11678.15</v>
       </c>
     </row>
     <row r="754">
@@ -49459,7 +49459,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>3706-312-CM26</t>
+          <t>501-281-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -49479,17 +49479,17 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -49518,13 +49518,13 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>11678.15</v>
+        <v>2654.13</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>1043030-43-CM26</t>
+          <t>1040758-120-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -49549,12 +49549,12 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -49583,7 +49583,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2350.03</v>
+        <v>2670.48</v>
       </c>
     </row>
     <row r="757">
@@ -49654,7 +49654,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>1040758-120-CM26</t>
+          <t>1043030-43-CM26</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -49679,12 +49679,12 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -49713,13 +49713,13 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>2670.48</v>
+        <v>2350.03</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>3497-422-CM26</t>
+          <t>1057506-4420-CM26</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -49744,12 +49744,12 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -49778,13 +49778,13 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>13895.27</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>3901-189-CM26</t>
+          <t>3497-422-CM26</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -49809,12 +49809,12 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -49843,13 +49843,13 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>10688.67</v>
+        <v>13895.27</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>1057506-4420-CM26</t>
+          <t>3901-189-CM26</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -49874,12 +49874,12 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -49908,13 +49908,13 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>3206.6</v>
+        <v>10688.67</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>1107279-110-CM26</t>
+          <t>3590-139-CM26</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -49934,17 +49934,17 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -49973,7 +49973,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>5406.69</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="763">
@@ -50044,7 +50044,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>3904-730-CM26</t>
+          <t>1107279-110-CM26</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -50069,12 +50069,12 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -50103,13 +50103,13 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>10813.38</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>3590-139-CM26</t>
+          <t>3904-730-CM26</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -50129,17 +50129,17 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -50168,7 +50168,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>2703.35</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="766">
@@ -50239,7 +50239,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>1060500-27-CM26</t>
+          <t>1107279-114-CM26</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -50259,17 +50259,17 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -50298,13 +50298,13 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>2703.02</v>
+        <v>12974.52</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>1107279-114-CM26</t>
+          <t>1107279-115-CM26</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -50363,7 +50363,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>12974.52</v>
+        <v>8649.68</v>
       </c>
     </row>
     <row r="769">
@@ -50434,7 +50434,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>1107279-115-CM26</t>
+          <t>1060500-27-CM26</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -50454,17 +50454,17 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -50493,7 +50493,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>8649.68</v>
+        <v>2703.02</v>
       </c>
     </row>
     <row r="771">
@@ -50564,7 +50564,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>1057512-691-CM26</t>
+          <t>3881-610-CM26</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -50584,17 +50584,17 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -50623,13 +50623,13 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>3290.99</v>
+        <v>17771.34</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>3496-158-CM26</t>
+          <t>3829-95-CM26</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -50649,17 +50649,17 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -50688,13 +50688,13 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>2742.49</v>
+        <v>3290.99</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>4329-477-CM26</t>
+          <t>1057512-691-CM26</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -50714,17 +50714,17 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ñiquen</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -50753,13 +50753,13 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>10969.96</v>
+        <v>3290.99</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>3881-610-CM26</t>
+          <t>3496-158-CM26</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -50779,17 +50779,17 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -50818,13 +50818,13 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>17771.34</v>
+        <v>2742.49</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>3829-95-CM26</t>
+          <t>4329-477-CM26</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -50849,12 +50849,12 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -50883,7 +50883,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>3290.99</v>
+        <v>10969.96</v>
       </c>
     </row>
     <row r="777">
@@ -51019,7 +51019,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>1043046-86-CM26</t>
+          <t>3786-97-CM26</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -51039,17 +51039,17 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>62.000.450-2</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -51078,13 +51078,13 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>2345.81</v>
+        <v>2510.09</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>3786-97-CM26</t>
+          <t>3449-107-CM26</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -51104,17 +51104,17 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>2510.09</v>
+        <v>3601.44</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>3449-107-CM26</t>
+          <t>1043046-86-CM26</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -51174,12 +51174,12 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>62.000.450-2</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -51208,7 +51208,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>3601.44</v>
+        <v>2345.81</v>
       </c>
     </row>
     <row r="782">
@@ -51799,7 +51799,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>1057506-4523-CM26</t>
+          <t>3706-369-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -51824,12 +51824,12 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>4332.61</v>
+        <v>10831.54</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>3706-369-CM26</t>
+          <t>1057506-4523-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -51889,12 +51889,12 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -51923,7 +51923,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>10831.54</v>
+        <v>4332.61</v>
       </c>
     </row>
     <row r="793">
@@ -52059,7 +52059,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>3841-146-CM26</t>
+          <t>4123-387-CM26</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -52079,17 +52079,17 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -52118,13 +52118,13 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>2350.65</v>
+        <v>3279.98</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>4123-387-CM26</t>
+          <t>3841-146-CM26</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -52144,17 +52144,17 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
@@ -52183,7 +52183,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>3279.98</v>
+        <v>2350.65</v>
       </c>
     </row>
     <row r="797">
@@ -52839,7 +52839,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>3590-170-CM26</t>
+          <t>3588-438-CM26</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -52859,7 +52859,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
@@ -52898,13 +52898,13 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>5336.98</v>
+        <v>10673.95</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>3588-438-CM26</t>
+          <t>3590-170-CM26</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -52924,7 +52924,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
@@ -52963,7 +52963,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>10673.95</v>
+        <v>5336.98</v>
       </c>
     </row>
     <row r="809">
@@ -53034,7 +53034,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>4519-253-CM26</t>
+          <t>4364-482-CM26</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -53059,12 +53059,12 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
@@ -53093,13 +53093,13 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>6427.63</v>
+        <v>3213.82</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>3881-710-CM26</t>
+          <t>1294449-73-CM26</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -53124,12 +53124,12 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>69.141.000-5</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
@@ -53158,13 +53158,13 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>22145.07</v>
+        <v>37494.51</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>1294449-73-CM26</t>
+          <t>4519-253-CM26</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -53189,12 +53189,12 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -53223,13 +53223,13 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>37494.51</v>
+        <v>6427.63</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>4364-482-CM26</t>
+          <t>3881-710-CM26</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -53254,12 +53254,12 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.141.000-5</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
@@ -53288,7 +53288,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>3213.82</v>
+        <v>22145.07</v>
       </c>
     </row>
     <row r="814">
@@ -54659,7 +54659,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>3599-350-CM26</t>
+          <t>5568-160-CM26</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -54679,17 +54679,17 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>69.140.202-9</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
@@ -54718,13 +54718,13 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>5177.54</v>
+        <v>2588.77</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>1057508-2405-CM26</t>
+          <t>3599-350-CM26</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -54749,12 +54749,12 @@
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.202-9</t>
         </is>
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
@@ -54783,13 +54783,13 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>37278.27</v>
+        <v>5177.54</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>5568-160-CM26</t>
+          <t>1048606-34-CM26</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -54809,17 +54809,17 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>62.000.540-1</t>
         </is>
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -54848,13 +54848,13 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>2588.77</v>
+        <v>2241.39</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>1048606-34-CM26</t>
+          <t>1057508-2405-CM26</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -54879,12 +54879,12 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>62.000.540-1</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -54913,13 +54913,13 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>2241.39</v>
+        <v>37278.27</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>3829-144-CM26</t>
+          <t>4256-270-CM26</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -54944,12 +54944,12 @@
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
@@ -54978,13 +54978,13 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>3111.71</v>
+        <v>2593.09</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>4256-270-CM26</t>
+          <t>3829-144-CM26</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -55009,12 +55009,12 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -55043,7 +55043,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>2593.09</v>
+        <v>3111.71</v>
       </c>
     </row>
     <row r="841">
@@ -55959,7 +55959,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>4521-126-CM26</t>
+          <t>3590-192-CM26</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -55979,17 +55979,17 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>69.250.602-2</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
@@ -56018,13 +56018,13 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>7868.3</v>
+        <v>4087.43</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>3590-192-CM26</t>
+          <t>4521-126-CM26</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -56044,17 +56044,17 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.250.602-2</t>
         </is>
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
@@ -56083,13 +56083,13 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>4087.43</v>
+        <v>7868.3</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>4123-442-CM26</t>
+          <t>3588-520-CM26</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -56109,17 +56109,17 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -56148,13 +56148,13 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>3058.76</v>
+        <v>11215.45</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>3588-520-CM26</t>
+          <t>4123-442-CM26</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -56174,17 +56174,17 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
@@ -56213,7 +56213,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>11215.45</v>
+        <v>3058.76</v>
       </c>
     </row>
     <row r="859">
@@ -56739,7 +56739,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>1057506-4806-CM26</t>
+          <t>1294449-86-CM26</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -56754,7 +56754,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -56764,12 +56764,12 @@
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -56798,13 +56798,13 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>3071.19</v>
+        <v>35766.84</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>3841-193-CM26</t>
+          <t>4252-301-CM26</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -56819,7 +56819,7 @@
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -56829,12 +56829,12 @@
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -56863,13 +56863,13 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>10237.3</v>
+        <v>16350.56</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>3784-578-CM26</t>
+          <t>1057506-4806-CM26</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -56894,12 +56894,12 @@
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -56928,71 +56928,201 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>10237.3</v>
+        <v>3071.19</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
+          <t>3841-193-CM26</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>69.141.600-3</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M870" s="2" t="n">
+        <v>10237.3</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>3784-578-CM26</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>69.150.200-7</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M871" s="2" t="n">
+        <v>10237.3</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
           <t>4157-1038-CM26</t>
         </is>
       </c>
-      <c r="B870" t="inlineStr">
+      <c r="B872" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C870" t="inlineStr">
+      <c r="C872" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr">
+      <c r="D872" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E870" t="inlineStr">
+      <c r="E872" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F870" t="inlineStr">
+      <c r="F872" t="inlineStr">
         <is>
           <t>69.141.700-K</t>
         </is>
       </c>
-      <c r="G870" t="inlineStr">
+      <c r="G872" t="inlineStr">
         <is>
           <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
-      <c r="H870" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I870" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J870" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K870" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L870" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M870" s="2" t="n">
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M872" s="2" t="n">
         <v>2534.01</v>
       </c>
     </row>
